--- a/body_image_training_leads.xlsx
+++ b/body_image_training_leads.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$M$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$N$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,22 +495,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -536,45 +537,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Why Body Image Training Fits</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Who to Contact (Role)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Contact Name</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Date Contacted</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -601,33 +607,38 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>Largest system in the region with a strong whole-person care mission. Weight bias training fits their patient experience goals.</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Clinical Education / Nursing Professional Development; Patient Experience</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>adventhealth.com</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -650,33 +661,38 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>Large nursing and physician workforce, ongoing patient experience and DEI training needs.</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Center for Learning / Nursing Education; Patient Experience Officer</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>orlandohealth.com</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -699,33 +715,38 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>Pregnancy and postpartum care is full of weight talk. Body-positive language directly improves patient trust.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Nurse Educator, Women's Services; Patient Experience</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>orlandohealth.com</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -748,33 +769,38 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>Pediatric weight conversations shape kids' lifelong body image. Staff need tools for these talks with kids and parents.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Clinical Education; Pediatric Weight Management Program Lead</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>nemours.org</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -797,33 +823,38 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>Serves a diverse, underserved community. Inclusive care training supports patient satisfaction scores.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Director of Education; Chief Nursing Officer</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>hcafloridahealthcare.com</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -846,33 +877,38 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>Regional system with residency programs that need communication and bias training content.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Graduate Medical Education Office; Nursing Education</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>mylrh.org</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -895,33 +931,38 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>Academic health system with grand rounds and staff CE programming.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Office of Diversity &amp; Inclusion; Grand Rounds Coordinators</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>ufhealth.org</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -944,33 +985,38 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>Academic medical center with bariatric and women's programs where weight stigma training applies.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Nursing Professional Development; Bariatric Program Director</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>tgh.org</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -993,33 +1039,38 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>Statewide hospital association that offers education to member hospitals. One yes reaches many hospitals.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Education &amp; Events Director</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>fha.org</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1042,33 +1093,38 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>Federally qualified health center serving low-income patients. Medical, dental, and behavioral staff all benefit.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>CEO; Director of Clinical Operations</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>obfh.org</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1091,33 +1147,38 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>Large FQHC network across Orange, Lake, and Seminole with family medicine and OB staff.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>HR / Training Director; Chief Medical Officer</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>chcfl.org</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1140,33 +1201,38 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>FQHC in Seminole County. Ties to her City of Sanford work.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>CEO; Director of Quality &amp; Training</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>mytruehealth.org</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1189,33 +1255,38 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>Free clinics run by volunteer clinicians. Volunteer training is a natural entry point.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Volunteer Services Director; Medical Director</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>shepherdshope.org</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1238,33 +1309,38 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>Faith-based medical home for uninsured families. Values-driven, whole-person care.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Executive Director; Clinical Director</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>gracemedicalhome.org</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1287,33 +1363,38 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>Large behavioral health provider. Body image overlaps with depression, anxiety, and disordered eating.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Clinical Training Director</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>aspirehealthpartners.com</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1336,33 +1417,38 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>Maternal and infant health. Home visitors and educators talk to pregnant women about weight and nutrition.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Executive Director; Program Manager (verify site, ph 407-228-1478)</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>(verify)</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1385,33 +1471,38 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>Reproductive care where weight talk often comes up. Inclusive care is core to their mission.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Education &amp; Training Director</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>plannedparenthood.org</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1434,33 +1525,38 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>Runs WIC and nutrition services where body image and weight messaging matter.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>WIC / Nutrition Services Director; Staff Development</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>orange.floridahealth.gov</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1483,33 +1579,38 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>Trains future physicians. Weight bias and inclusive care fit into curriculum and student wellness.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Office of Diversity &amp; Inclusion; Clinical Skills Course Director</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>med.ucf.edu</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1532,33 +1633,38 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
           <t>Large nursing program. Guest lecture or workshop for students and faculty.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Associate Dean; Simulation / Clinical Faculty</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>nursing.ucf.edu</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1581,33 +1687,38 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>Community-based med school campus in Orlando with a patient-centered focus.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Regional Campus Dean; Student Affairs</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>med.fsu.edu</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1630,33 +1741,38 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>Academic medical school with wellness and professionalism curriculum.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Office of Diversity &amp; Inclusion; Curriculum Office</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>health.usf.edu</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1679,33 +1795,38 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>Large med school. Grand rounds and curriculum speaker slots.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Office of Diversity, Equity &amp; Inclusion</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>med.ufl.edu</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1728,33 +1849,38 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>Health sciences university (nursing, PA, OT, imaging). Whole-person care mission.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Dean of Nursing; Student Success / Events</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>ahu.edu</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1777,33 +1903,38 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>Large pipeline of local nurses, dental hygienists, and techs.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Dean of Nursing; Health Sciences Dean</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>valenciacollege.edu</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1826,33 +1957,38 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>Past speaking engagement. Warm relationship and HBCU nursing pipeline.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Dean of Nursing</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>cookman.edu</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1875,33 +2011,38 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>Osteopathic, whole-person philosophy. Campuses in South FL and Tampa Bay.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Office of Diversity; Student Affairs</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>osteopathic.nova.edu</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1924,33 +2065,38 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>Counselors work with students on body image and eating concerns daily.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>CAPS Director; Outreach Coordinator</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>caps.sdes.ucf.edu</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1973,33 +2119,38 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>Campus wellness team serving a student body with high body image pressure.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Wellness Center Director</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>rollins.edu</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -2022,33 +2173,38 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>Dietitians are on the front line of weight conversations. Weight-inclusive practice is a hot CE topic.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Continuing Education / Annual Symposium Chair</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>eatrightflorida.org</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2071,33 +2227,38 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>Family docs have the most weight conversations. Annual conference and CME webinars.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>CME / Education Director</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>fafp.org</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2120,33 +2281,38 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>Statewide nurse association with CE offerings and regional chapters.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Education Director; Regional Chapter Presidents</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>floridanurse.org</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -2169,33 +2335,38 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>Pediatricians talk to kids and parents about weight. Stigma-free language is a current AAP focus.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Education / Meetings Director</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>fcaap.org</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2218,33 +2389,38 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>Statewide physician association with CME programming.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>CME / Education Department</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>flmedical.org</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2267,33 +2443,38 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>OB-GYNs see weight stigma affect prenatal and gynecologic care.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Section Chair; Annual Meeting Planner</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>acog.org</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2316,33 +2497,38 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>Psychologists treat body image issues. CE workshop or convention session.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>CE Committee; Convention Chair</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>flapsych.com</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2365,33 +2551,38 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>Public health workforce writes messaging on weight and nutrition. Conference session fit.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Conference / Education Committee</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>fpha.org</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -2414,33 +2605,38 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>Florida-based eating disorder nonprofit that already trains professionals. Partnership or co-training.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Executive Director; Education Programs</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>allianceforeatingdisorders.com</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2463,33 +2659,38 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>Runs professional education and awareness weeks. Speaker and partner opportunity.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Programs / Partnerships Team</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>nationaleatingdisorders.org</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -2512,33 +2713,38 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>Eating disorder access nonprofit focused on equity. Strong values match.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>Partnerships / Programs Director</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>theprojectheal.org</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -2561,33 +2767,38 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>Local eating disorder treatment center. Hosts professional trainings and staff in-services.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Site Director; Professional Training (Renfrew Foundation)</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>renfrewcenter.com</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -2610,33 +2821,38 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>Large treatment network with clinician education programming.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>Clinical Education / Professional Relations</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>eatingrecoverycenter.com</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2659,33 +2875,38 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>Florida-based national org fighting weight bias. Staff and member education, conference speaker.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Education / Events Director</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>obesityaction.org</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="I44" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -2708,33 +2929,38 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>Weight-inclusive health org. Partner, speaker, or co-branded training.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Board / Programs Committee</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>asdah.org</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2757,33 +2983,38 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>Clinicians treating obesity need stigma-free communication skills.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Education / Conference Team</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>obesitymedicine.org</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr">
+      <c r="I46" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -2806,33 +3037,38 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>Women physicians and students. Body image and inclusive care fit their women's health focus.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Programs / Conference Chair</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>amwa-doc.org</t>
         </is>
       </c>
-      <c r="H47" s="6" t="inlineStr">
+      <c r="I47" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -2855,33 +3091,38 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>Major insurer with Florida Blue Centers, nurses, and health coaches. Also employee wellness.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Health &amp; Wellness / Clinical Training; Florida Blue Center Managers</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>floridablue.com</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -2904,33 +3145,38 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>School nurses and PE staff shape how kids see their bodies.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>Health Services Director; Professional Learning</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>ocps.net</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2953,33 +3199,38 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>Fitness and youth staff talk about bodies every day. Staff training plus member programming.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>VP of Healthy Living; Staff Training</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>ymcacf.org</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -3002,91 +3253,2846 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>Volunteer and staff training to support girls' confidence. Ties to her mentoring work.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>CEO; Volunteer Development</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>citrus-gs.org</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>Not Contacted</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>NYC Health + Hospitals</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Health System / Hospital</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Largest public health system in the US, in one of her top markets. Serves diverse patients who face weight stigma in care.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Workforce Development / Learning; Office of Diversity &amp; Inclusion</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>nychealthandhospitals.org</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Northwell Health</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Health System / Hospital</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>New Hyde Park / Long Island, NY</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Big NY system with a large internal learning institute and a focus on patient experience.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Center for Learning &amp; Innovation; Patient Experience</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>northwell.edu</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Grady Health System</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Health System / Hospital</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Atlanta safety-net hospital in one of her top markets. Serves mostly Black and low-income patients.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Nursing Education; Patient Experience</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>gradyhealth.org</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Emory Healthcare</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Health System / Hospital</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Academic system in Atlanta with women's health and bariatric programs.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Nursing Professional Development; Diversity &amp; Inclusion</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>emoryhealthcare.org</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Children's Healthcare of Atlanta</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Health System / Hospital</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Pediatric system with a well-known weight management program. Staff talk to kids and parents about weight daily.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Education; Strong4Life / Wellness Program Lead</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>choa.org</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Kaiser Permanente</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Health System / Hospital</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Oakland, CA (national)</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Huge integrated system with a strong equity focus and a large internal training budget.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>National Learning &amp; Development; Equity, Inclusion &amp; Diversity</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>kp.org</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Health System / Hospital</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Rochester, MN</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Top academic system with grand rounds and staff education programs.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Education Office; Office of Equity, Inclusion &amp; Diversity</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>mayoclinic.org</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Cleveland Clinic</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Health System / Hospital</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Cleveland, OH</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Known for patient experience leadership. Inclusive care fits their Empathy work.</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Office of Patient Experience; Nursing Education</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>clevelandclinic.org</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Johns Hopkins Medicine</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Health System / Hospital</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Baltimore, MD</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Academic system with strong health equity programming.</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Office of Diversity, Inclusion &amp; Health Equity</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>hopkinsmedicine.org</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Penn Medicine</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Health System / Hospital</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Home of the Center for Weight and Eating Disorders. Clinicians already care about this topic.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Center for Weight and Eating Disorders; Nursing Education</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>pennmedicine.org</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Mass General Brigham</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Health System / Hospital</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Large Boston system with an active eating disorders and weight center.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Learning &amp; Development; Health Equity Office</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>massgeneralbrigham.org</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Atrium Health</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Health System / Hospital</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte, NC</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Large Southeast system with a big nursing workforce.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Nursing Professional Development; Patient Experience</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>atriumhealth.org</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Ochsner Health</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Health System / Hospital</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>New Orleans, LA</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Gulf South system serving communities with high chronic disease rates.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Ochsner Learning; Patient Experience</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>ochsner.org</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Intermountain Health</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Health System / Hospital</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Large system known for clinical quality programs and staff education.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Caregiver Development; Patient Experience</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>intermountainhealthcare.org</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Providence</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Health System / Hospital</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Renton, WA (multi-state)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Faith-based system in 7 states with a whole-person care mission.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Caregiver Learning; Mission Integration</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>providence.org</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Children's Hospital of Philadelphia (CHOP)</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Health System / Hospital</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Top pediatric hospital with a Healthy Weight program and an eating disorder program.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Healthy Weight Program; Nursing Education</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>chop.edu</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Boston Children's Hospital</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Health System / Hospital</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Pediatric system with eating disorder and weight programs. Strong staff education culture.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Education; Adolescent Medicine</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>childrenshospital.org</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Texas Children's Hospital</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Health System / Hospital</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Largest US children's hospital with a pediatric weight management program.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Education; Patient &amp; Family Experience</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>texaschildrens.org</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Morehouse School of Medicine</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Medical / Nursing Education</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>HBCU med school in Atlanta focused on health equity. Strong values and market match.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Office of Student Affairs; Community Health / Curriculum</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>msm.edu</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Howard University College of Medicine</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Medical / Nursing Education</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>HBCU med school. Weight bias hits Black women hard in care.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Dean's Office; Student Affairs</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>medicine.howard.edu</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Meharry Medical College</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Medical / Nursing Education</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Nashville, TN</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>HBCU medical, dental, and public health school.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Office of Academic Affairs; Student Affairs</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>mmc.edu</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Harvard Medical School</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Medical / Nursing Education</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Past Harvard speaking engagement. Warm intro angle for a staff or student workshop.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Office for Diversity Inclusion &amp; Community Partnership</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>hms.harvard.edu</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Johns Hopkins School of Nursing</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Medical / Nursing Education</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Baltimore, MD</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Top nursing school with a health equity focus.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Office of Diversity, Equity &amp; Inclusion</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>nursing.jhu.edu</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Columbia University School of Nursing</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Medical / Nursing Education</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>NYC nursing school in her top market.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Office of Diversity &amp; Cultural Affairs</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>nursing.columbia.edu</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Emory Nell Hodgson Woodruff School of Nursing</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Medical / Nursing Education</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Atlanta nursing school in her top market.</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Office of Diversity &amp; Inclusion; Student Affairs</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>nursing.emory.edu</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Icahn School of Medicine at Mount Sinai</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Medical / Nursing Education</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>NYC med school with a strong anti-racism and equity curriculum.</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Office for Diversity &amp; Inclusion</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>icahn.mssm.edu</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>UCSF School of Medicine</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Medical / Nursing Education</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Med school with a strong focus on health equity and bias training.</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Differences Matter Initiative; Curriculum Office</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>medschool.ucsf.edu</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>UConn Rudd Center for Food Policy &amp; Health</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Medical / Nursing Education</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Hartford, CT</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Leading research center on weight bias that publishes training tools for clinicians. Partner or co-training.</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Weight Bias &amp; Stigma Research Team</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>uconnruddcenter.org</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>American Academy of Family Physicians</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Professional Association (CE credits)</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Leawood, KS (national)</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>National family doctor group with huge CME programs. Weight stigma is a current topic.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>CME / Conference Programming</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>aafp.org</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Academy of Nutrition and Dietetics</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Professional Association (CE credits)</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Chicago, IL (national)</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>National dietitian group. FNCE conference and CE webinars.</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>FNCE Program Planning; Continuing Education</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>eatright.org</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>American Nurses Association</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Professional Association (CE credits)</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Silver Spring, MD (national)</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>National nurses group with webinars and CE.</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>ANA Enterprise Continuing Education</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>nursingworld.org</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>American Academy of Pediatrics</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Professional Association (CE credits)</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Itasca, IL (national)</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>AAP updated its obesity guidance. Pediatricians need stigma-free language skills.</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Education / National Conference Planning</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>aap.org</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>American College of Obstetricians and Gynecologists (ACOG)</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Professional Association (CE credits)</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Washington, DC (national)</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>National OB-GYN group. Weight bias affects prenatal and gynecologic care.</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Education Division; Annual Meeting Planning</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>acog.org</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>American Psychological Association</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Professional Association (CE credits)</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Washington, DC (national)</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Psychologists treat body image issues. Convention session or CE webinar.</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Continuing Education Office; Convention Program</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>apa.org</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>National Black Nurses Association</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Professional Association (CE credits)</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Silver Spring, MD (national)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Black nurses group with local chapters and an annual conference. Strong mission fit.</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Conference Planning; Chapter Presidents</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>nbna.org</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>National Medical Association</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Professional Association (CE credits)</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Silver Spring, MD (national)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Oldest Black physician group. Annual convention and CME.</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Convention / CME Planning</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>nmanet.org</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Student National Medical Association</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Professional Association (CE credits)</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Washington, DC (national)</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Students of color in medical school. Annual conference and chapter workshops.</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Annual Medical Education Conference Planning; Chapter Leaders</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>snma.org</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Academy for Eating Disorders</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Professional Association (CE credits)</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Reston, VA (national)</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Global group of eating disorder professionals. Conference and webinar speaker.</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Education / Conference Committee</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>aedweb.org</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>International Association of Eating Disorders Professionals (iaedp)</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Professional Association (CE credits)</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>National (local chapters)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Certifies eating disorder clinicians. Chapters host local CE trainings.</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Chapter Presidents; Symposium Planning</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>iaedp.com</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>American College Health Association</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Professional Association (CE credits)</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Silver Spring, MD (national)</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Campus health and counseling staff deal with student body image daily.</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Annual Meeting / Professional Development</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>acha.org</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>National Association of School Nurses</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Professional Association (CE credits)</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Silver Spring, MD (national)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>School nurses do weight screenings and talk to kids about their bodies.</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Education / Conference Planning</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>nasn.org</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>American Physical Therapy Association</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Professional Association (CE credits)</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Alexandria, VA (national)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>PTs work hands-on with bodies of all sizes. Inclusive care training fits.</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Education / CE Department</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>apta.org</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Monte Nido</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Eating Disorder / Weight Bias Org</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Miami, FL HQ (national sites)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>National eating disorder treatment network with clinician trainings.</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Education / Professional Relations</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>montenido.com</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Center for Discovery</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Eating Disorder / Weight Bias Org</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>National (multi-state)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Eating disorder and mental health treatment network.</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Training; Professional Relations</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>centerfordiscovery.com</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Walden Behavioral Care</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Eating Disorder / Weight Bias Org</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Waltham, MA</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Eating disorder treatment provider in New England and Georgia.</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Training Director</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>waldenbehavioralcare.com</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>The Emily Program</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Eating Disorder / Weight Bias Org</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>St. Paul, MN (multi-state)</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Eating disorder treatment provider with regular professional education events.</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Professional Relations / Education</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>emilyprogram.com</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Multi-Service Eating Disorders Association (MEDA)</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Eating Disorder / Weight Bias Org</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Eating disorder nonprofit that runs professional training.</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Executive Director; Education Programs</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>medainc.org</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Planet Fitness</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Youth / Community / Employer</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Hampton, NH (national)</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Built on a Judgement Free Zone brand. Body-positive staff training fits their identity.</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Culture / Training; Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>planetfitness.com</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>YMCA of the USA</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Youth / Community / Employer</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Chicago, IL (national)</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>National Y supports 2,600+ local Ys with staff training. One yes can scale.</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Healthy Living / Learning &amp; Development</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>ymca.org</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Girl Scouts of the USA</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Youth / Community / Employer</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY (national)</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Volunteer and staff training to build girls' confidence. Ties to her mentoring work.</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Program / Volunteer Development</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>girlscouts.org</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M51"/>
+  <autoFilter ref="A1:N101"/>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="J2:J101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Not Contacted,Emailed,Follow-up Sent,Replied,Call Booked,Proposal Sent,Won,Not a Fit"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId99"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3114,14 +6120,14 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Brand for this list: Danielle Adams (organizations hiring expertise). Offer: staff training through the Institute for Body Image.</t>
+          <t>100 leads: rows 1-50 Florida, rows 51-100 national (filter by Region). Brand for this list: Danielle Adams (organizations hiring expertise). Offer: staff training through the Institute for Body Image.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Priority A = Central Florida and/or strongest fit, reach out first. B = good fit, second wave. C = national/longer shot.</t>
+          <t>Priority A = Central Florida, her top markets (NYC, Atlanta), warm ties (Harvard, HBCUs), or strongest mission fit, reach out first. B = good fit, second wave. C = national/longer shot.</t>
         </is>
       </c>
     </row>
